--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-e0e166b4-0f77-478d-9062-de0034d98ce0.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-e0e166b4-0f77-478d-9062-de0034d98ce0.xlsx
@@ -1142,90 +1142,6 @@
     <t>Consent.category.text</t>
   </si>
   <si>
-    <t>Consent.category:resultType</t>
-  </si>
-  <si>
-    <t>resultType</t>
-  </si>
-  <si>
-    <t>http://fhir.de/ConsentManagement/ValueSet/ResultType</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.id</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.extension</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.id</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.extension</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.system</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.version</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.code</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.display</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.text</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType</t>
-  </si>
-  <si>
-    <t>templateType</t>
-  </si>
-  <si>
-    <t>http://fhir.de/ConsentManagement/ValueSet/TemplateType</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.id</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.extension</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.id</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.extension</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.system</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.version</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.code</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.display</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.text</t>
-  </si>
-  <si>
     <t>Consent.category:mii</t>
   </si>
   <si>
@@ -1271,6 +1187,90 @@
   </si>
   <si>
     <t>Consent.category:mii.text</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType</t>
+  </si>
+  <si>
+    <t>resultType</t>
+  </si>
+  <si>
+    <t>http://fhir.de/ConsentManagement/ValueSet/ResultType</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.id</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.extension</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.id</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.extension</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.system</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.version</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.code</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.display</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.text</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType</t>
+  </si>
+  <si>
+    <t>templateType</t>
+  </si>
+  <si>
+    <t>http://fhir.de/ConsentManagement/ValueSet/TemplateType</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.id</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.extension</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.id</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.extension</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.system</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.version</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.code</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.display</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.text</t>
   </si>
   <si>
     <t>Consent.patient</t>
@@ -9995,10 +9995,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>88</v>
@@ -10028,7 +10028,7 @@
         <v>76</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>76</v>
+        <v>364</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>76</v>
@@ -10043,11 +10043,13 @@
         <v>76</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>364</v>
+        <v>332</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>76</v>
@@ -10325,7 +10327,7 @@
         <v>87</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>88</v>
@@ -11377,7 +11379,7 @@
         <v>76</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>144</v>
+        <v>222</v>
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
@@ -12663,10 +12665,10 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>88</v>
@@ -12696,7 +12698,7 @@
         <v>76</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>392</v>
+        <v>76</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>76</v>
@@ -12713,11 +12715,9 @@
       <c r="X92" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="Y92" t="s" s="2">
-        <v>331</v>
-      </c>
+      <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>332</v>
+        <v>392</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>76</v>
@@ -12995,7 +12995,7 @@
         <v>87</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>88</v>
